--- a/outputs/evaluation.xlsx
+++ b/outputs/evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\File\Kuliah\Semester 8\Generative AI\UAS\ai-healthy-assistant\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8333E51D-34E4-4B98-B414-27F0DB56707D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5224AC-2F89-439E-BCBA-349AEFA5CEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,16 +69,20 @@
     <t>Apa manfaat tidur cukup?</t>
   </si>
   <si>
-    <t>Tidur yang cukup memiliki banyak manfaat untuk kesehatan. Mari kita uraikan beberapa dari mereka:
-1. Tidur mencapai tahap REM (Rasionalized Electroencephalographic) membantu otak dalam proses pemrosesan informasi dan regenerasi sel-sel saraf.
-2. Peningkatan energi dan daya tahan terhadap cedera saat aktivitas fisik karena sistem imunitas menjadi lebih kuat.
-3. Mengurangi risiko serangan jantung dan stroke akibat tekanan darah tinggi.
-4. Menyediakan ruang kosong untuk pembentukan hormon-growth yang sangat dibutuhkan oleh anak-anak dan remaja untuk perkembangan.
-Saran Kepentingannya:
-Ingatlah bahwa tiap orang memiliki kebutuhan tidur sendiri-sendiri, sehingga cobalah untuk merencanakan jam tidur Anda agar cukup. Untuk melihat apakah tidurmu sudah cukup, lihat apakah dirimu merasa segar ketika bangun paginya dan tidak lagi memerlukan istirahat</t>
-  </si>
-  <si>
-    <t>outputs/audio/output_1781578967.wav</t>
+    <t xml:space="preserve">Tidur yang cukup memiliki beberapa manfaat untuk kesehatan. 
+1. Tidur menciptakan energi dan meningkatkan kemampuan fungsional dalam melakukan aktivitas harian.
+2. Mempercepat proses pemulihan fisik dan mental, sehingga membuatmu lebih segar dan siap meraih tujuan-tujuan baru.
+3. Mengurangi resiko terkena masalah kesehatan kronis seperti tekanan darah tinggi, kolesterol jahat, hiperlipemia, serta penyakit jantung dan stroke.
+4. Melancarkan ritme biologis tubuh dan membangkitkan hormon produksi.
+5. Menyediakan ruang kosong untuk perkembangan otak dan pembentukan memory baru.
+6. Memberikan kesempatan kepada sistem imunitas untuk bekerja efektif melawan infeksi dan virus.
+7. Dapat juga membantu memperlambat progresus keriput dan fleksibilitas kulit.
+8. Meningkatkan mood dan daya ingat.
+9. Kurangi rasa cemas dan stres.
+</t>
+  </si>
+  <si>
+    <t>outputs/audio/output_1781582378.wav</t>
   </si>
   <si>
     <t>Kemenkes RI</t>
@@ -87,57 +91,52 @@
     <t>Berapa kebutuhan air putih harian?</t>
   </si>
   <si>
-    <t>Mengenai kebutuhan air putih harian, disampaikan bahwa ratarata orang dewasa dianjurkan minum sekitar 2 liter atau 8 gelas air per hari. 
-1. Pastikan kamu mencapai target ini. Karena tinggi suhu dan aktivitas bisa meninggalkan dehidrasi cepat, penting untuk tetap merencanakan jumlah air yang akan diminum tiap hari.
-2. Hindari minuman bersoda dan alkohol karena mereka sering kali melemahkan tubuh dan membuatmu kehilangan kadar air daripadanya.
-3. Buatlah rutinitas minum air agar menjadi biasa. Misalnya, gunakan botol besar untuk mendongkrak semangat minum selama satu minggu berturut-turut.
-4. Selalu ingat bahwa rencana ini harus ditentukan sendiri tergantung pada aktivitas fisik, cuaca, serta lingkungan tempat tinggalmu.
-5. Apakah ada kondisi tertentu seperti sakit kepala atau demam? Dalam beberapa kasus, kekurangan air juga bisa menjadi</t>
-  </si>
-  <si>
-    <t>outputs/audio/output_1781579066.wav</t>
+    <t>Mengenai kebutuhan air putih harian, tergantung pada faktor-faktor seperti jenis kelamin, tinggi badan, aktivitas fisik, dan suhu lingkungan. Untuk generalisasi, kita bisa fokus pada rekomendasi rata-rata yang telah disampaikan sebelumnya. 
+1. Orang Dewasa Umumnya Direncanakan Mengkonsumsi Sekitar 2 Liter Air Per Hari: Ini mencerminkan rekomendasi bahwa mereka mendapatkan cukup jumlah air untuk memenuhi keperluan normal mereka dalam satu hari. Namun, ini juga harus ditentukan oleh individu sendiri berdasarkan suasana hatinya dan efeknya pada tubuh.
+2. Anak Usia Dari Tahun Keempat Sampai Delapan Bulanan Memerlukan Kebutuhan Cairan Lebih Tinggi: Menurut IOM, anak-anak usia 4 sampai delapan tahun membutuhkan hingga 1,7 litar air per hari, sehingga penting bagi para orang tua untuk memastikan anak-anak Anda selalu bersedia minum</t>
+  </si>
+  <si>
+    <t>outputs/audio/output_1781582475.wav</t>
   </si>
   <si>
     <t>Apa dampak kurang tidur?</t>
   </si>
   <si>
-    <t>Kurang tidur bisa membuat kamu merasakan lelah, rewel, kesulitan fokus, dan mood jelek. 
-1. Kurangi jam kerjamu untuk mendapatkan waktu istirahat cukup. 
-2. Cobalah melakukan aktivitas relaksasi seperti mandi hangat atau yoga beberapa saat sebelum tidur.
-3. Hindari makan besar atau minuman manis tepat sebelum tidur karena bisa merepotkan sistem pencernaanmu.
-4. Buat rutinitas tidur-menyegar setiap hari agar tubuh cepat adaptif.</t>
-  </si>
-  <si>
-    <t>outputs/audio/output_1781579148.wav</t>
-  </si>
-  <si>
-    <t>Alodokter, Kemenkes RI</t>
+    <t>Maaf, saya hanya dapat membantu pertanyaan yang berkaitan dengan kesehatan dan pola hidup sehat.</t>
+  </si>
+  <si>
+    <t>outputs/audio/output_1781582541.wav</t>
+  </si>
+  <si>
+    <t>Kemenkes RI, Alodokter</t>
   </si>
   <si>
     <t>Bagaimana cara menjaga hidrasi tubuh?</t>
   </si>
   <si>
-    <t>Banyak orang sering lupa tentang pentingnya hidrasi. Untuk menjaga kekebalan tubuh dan kualitas hidupmu, ikuti tips ini:
-1. **Konsumsilah Air Putih**: Minumlah minimal 8 gelas air putih dalam sehari. Pastikan juga mencoba variasi jus buah segar atau teh herbal tanpa tambahan gula untuk meningkatkan rasa dan nutrisinya.
-2. **Hidrasi Selama Aktivitas**: Saat melakukan aktivitas fisik seperti jogging, berenang, ataupun bekerja di ruangan panas, selalu ingat untuk minum lebih banyak air. Ini akan membantu melawan dehidrasi akibat persipiran tubuh.
-3. **Tetap Konstan Mengkonsumsi Cairan**: Karena cairan bisa keluar lewat urine, bersin, batuk, dan urin, maka sangat penting untuk memastikan tubuh selalu diberi suplai yang baru. 
-4. **Waspadalah Tentang Dehidrasi** : Cek apakah kamu sudah tersedia cukup cairan.</t>
-  </si>
-  <si>
-    <t>outputs/audio/output_1781579245.wav</t>
+    <t>1. Konsumsilah banyak air putih selama seharian. Cobalah minum secarik gelas minimal satu sampai dua liter air dalam sehari.
+2. Perbanyak konsumsi buah-buahan dan sayuran yang tinggi akan vitamin C karena mereka juga bisa meningkatkan imunitas tubuhmu.
+3. Hindari alkohol dan teh hitam panas, dikarenakan kedua hal ini sering membuat kulit menjadi lebih kering dan bisa memicu dehidrasi.
+4. Pastikan untuk selalu minum air ketika melakukan aktivitas fisik intens seperti jogging atau berenang. Ini penting demi menciptakan rasio antara ekspektansi cairan dan pencampuran dengan udara hangat.
+5. Ingatlah bahwa gejalanya bisa sangat variatif, mulai dari sensasi lembab hingga sakit kepala, demam, atau mata tebal. Jika gejala semakin parah, minta bantuan dokter.
+6. Lakukan self-check-up rutin. Tanyakan dirimu sendiri apakah sudah cukup cairan? Apa saja re</t>
+  </si>
+  <si>
+    <t>outputs/audio/output_1781582652.wav</t>
   </si>
   <si>
     <t>Apakah minum kopi berlebihan berbahaya?</t>
   </si>
   <si>
-    <t>Ya, minum kopi berlebihan bisa berbahaya. Kafein dari kopi memiliki efek stimulan yang tinggi. Untuk kamu yang sudah terkena aritmia, minum kopi berlebihan bisa memperburuk gejalanya karena akan meningkatkan tekanan jantung. 
-1. Kurangi jumlah kopi yang dikonsumsi untuk mulai merasakan manfaatnya. Mulailah dengan reduksi sedikit demi sedikit hingga mencapai batasanmu sendiri tanpa adanya reaksi negatif seperti rileksasi terlalu cepat setelah minum kopi.
-2. Alternati kopi dengan teh hijau atau buah-buahan lainnya yang rendah kafein tetapi masih dapat memberikan energi positif. Misalnya, mangga segar saat pagi hari.
-3. Cobalah variasi waktu pemakaian kopi agar notifikasi jantung tidak selalu 'mobilir' ketika mendapatkan stimulan ini.
-4. Selain itu, pastikan juga kamu cukup istirahat dan tidur baik supaya fisik dan emosional</t>
-  </si>
-  <si>
-    <t>outputs/audio/output_1781579342.wav</t>
+    <t>Ya, minum kopi berlebihan bisa memiliki efek negatif tergantung pada kondisi kesehatanmu. Mari kita diskusikan hal-hal penting tentang itu:
+1. Untuk Penderita Aritmia: Konsumsi kopi berlebihan bisa meningkatkan tekanan jantung dan frekuensinya, yang merupakan isu besar untuk mereka yang sudah memiliki masalah ini. 
+2. Kerutan Wajah: Kafein juga bisa melemahkan pembuluh darah kecil di kulit, yang kemudian merangsang produksi sel-silinder kolagen dan elastin, faktor respon normal terhadap dehidrasi. Ini bisa menyebabkan timbunan lemak di kulit dan membuat area tertentu tampak lebih tua cepat.
+3. Kurang Tidur: Dalam jumlah banyak, kafein bisa mempengaruhi kualitas tidur malam. Itu bisa mengganggu siklus tidur Anda dan membuat kamu sulit bangun pagi setelahnya.
+Saran:
+1. Cobalah untuk mengontrol jumlah kopi yang dikonsum</t>
+  </si>
+  <si>
+    <t>outputs/audio/output_1781582755.wav</t>
   </si>
   <si>
     <t>Alodokter</t>
@@ -204,14 +203,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -340,11 +340,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.21875" customWidth="1"/>
-    <col min="2" max="2" width="219.44140625" customWidth="1"/>
+    <col min="2" max="2" width="242.21875" customWidth="1"/>
     <col min="3" max="3" width="32.44140625" customWidth="1"/>
     <col min="4" max="4" width="21.33203125" customWidth="1"/>
     <col min="5" max="5" width="9.109375" customWidth="1"/>
@@ -355,10 +355,10 @@
     <col min="10" max="10" width="20.44140625" customWidth="1"/>
     <col min="11" max="11" width="20.33203125" customWidth="1"/>
     <col min="12" max="12" width="22.6640625" customWidth="1"/>
-    <col min="13" max="13" width="78.5546875" customWidth="1"/>
+    <col min="13" max="13" width="83.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -398,211 +398,229 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:13" ht="171.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="264" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="3">
-        <v>0.56950000000000001</v>
-      </c>
-      <c r="F2" s="3">
-        <v>78.11</v>
-      </c>
-      <c r="G2" s="3">
-        <v>4</v>
-      </c>
-      <c r="H2" s="3">
-        <v>4</v>
-      </c>
-      <c r="I2" s="3">
+      <c r="E2" s="4">
+        <v>0.67520000000000002</v>
+      </c>
+      <c r="F2" s="4">
+        <v>93.95</v>
+      </c>
+      <c r="G2" s="4">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4">
         <v>3</v>
       </c>
-      <c r="J2" s="3">
-        <v>4</v>
-      </c>
-      <c r="K2" s="3">
-        <v>4</v>
-      </c>
-      <c r="L2" s="3">
-        <v>2.15</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="J2" s="4">
+        <v>4</v>
+      </c>
+      <c r="K2" s="4">
+        <v>4</v>
+      </c>
+      <c r="L2" s="4">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:13" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3">
-        <v>0.78969999999999996</v>
-      </c>
-      <c r="F3" s="3">
-        <v>96.5</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="E3" s="4">
+        <v>0.83819999999999995</v>
+      </c>
+      <c r="F3" s="4">
+        <v>94.03</v>
+      </c>
+      <c r="G3" s="4">
         <v>5</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <v>5</v>
       </c>
-      <c r="I3" s="3">
-        <v>4</v>
-      </c>
-      <c r="J3" s="3">
-        <v>4</v>
-      </c>
-      <c r="K3" s="3">
-        <v>4</v>
-      </c>
-      <c r="L3" s="3">
-        <v>2.19</v>
-      </c>
-      <c r="M3" s="1" t="s">
+      <c r="I3" s="4">
+        <v>4</v>
+      </c>
+      <c r="J3" s="4">
+        <v>4</v>
+      </c>
+      <c r="K3" s="4">
+        <v>4</v>
+      </c>
+      <c r="L3" s="4">
+        <v>2.08</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:13" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3">
-        <v>0.70779999999999998</v>
-      </c>
-      <c r="F4" s="3">
-        <v>80.05</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="E4" s="4">
+        <v>0.30790000000000001</v>
+      </c>
+      <c r="F4" s="4">
+        <v>64.31</v>
+      </c>
+      <c r="G4" s="4">
         <v>5</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <v>5</v>
       </c>
-      <c r="I4" s="3">
-        <v>4</v>
-      </c>
-      <c r="J4" s="3">
-        <v>4</v>
-      </c>
-      <c r="K4" s="3">
-        <v>4</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1.08</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="I4" s="4">
+        <v>4</v>
+      </c>
+      <c r="J4" s="4">
+        <v>4</v>
+      </c>
+      <c r="K4" s="4">
+        <v>4</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="145.19999999999999" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="3">
-        <v>0.65480000000000005</v>
-      </c>
-      <c r="F5" s="3">
-        <v>95.65</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="E5" s="4">
+        <v>0.5302</v>
+      </c>
+      <c r="F5" s="4">
+        <v>110.06</v>
+      </c>
+      <c r="G5" s="4">
         <v>5</v>
       </c>
-      <c r="H5" s="3">
-        <v>4</v>
-      </c>
-      <c r="I5" s="3">
+      <c r="H5" s="4">
+        <v>4</v>
+      </c>
+      <c r="I5" s="4">
         <v>3</v>
       </c>
-      <c r="J5" s="3">
-        <v>4</v>
-      </c>
-      <c r="K5" s="3">
-        <v>4</v>
-      </c>
-      <c r="L5" s="3">
-        <v>1.96</v>
-      </c>
-      <c r="M5" s="3" t="s">
+      <c r="J5" s="4">
+        <v>4</v>
+      </c>
+      <c r="K5" s="4">
+        <v>4</v>
+      </c>
+      <c r="L5" s="4">
+        <v>2.27</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:13" ht="118.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="132" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="3">
-        <v>0.81950000000000001</v>
-      </c>
-      <c r="F6" s="3">
-        <v>94.94</v>
-      </c>
-      <c r="G6" s="3">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3">
+      <c r="E6" s="4">
+        <v>0.83489999999999998</v>
+      </c>
+      <c r="F6" s="4">
+        <v>100.92</v>
+      </c>
+      <c r="G6" s="4">
+        <v>4</v>
+      </c>
+      <c r="H6" s="4">
         <v>3</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <v>3</v>
       </c>
-      <c r="J6" s="3">
-        <v>4</v>
-      </c>
-      <c r="K6" s="3">
-        <v>4</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1.95</v>
-      </c>
-      <c r="M6" s="3" t="s">
+      <c r="J6" s="4">
+        <v>4</v>
+      </c>
+      <c r="K6" s="4">
+        <v>4</v>
+      </c>
+      <c r="L6" s="4">
+        <v>1.88</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
